--- a/Documents/Design/스테이지/맵 핵심 오브젝트.xlsx
+++ b/Documents/Design/스테이지/맵 핵심 오브젝트.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2025-2_Space1\Documents\Design\스테이지\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2872F98-538E-417B-9CFC-F40529F8E24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="29265" yWindow="0" windowWidth="22320" windowHeight="15435" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="상호작용 오브젝트" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="환경 및 기믹 오브젝트" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="획득 아이템" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="맵" sheetId="4" r:id="rId7"/>
+    <sheet name="상호작용 오브젝트" sheetId="1" r:id="rId1"/>
+    <sheet name="환경 및 기믹 오브젝트" sheetId="2" r:id="rId2"/>
+    <sheet name="획득 아이템" sheetId="3" r:id="rId3"/>
+    <sheet name="맵" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="55">
   <si>
     <t>오브젝트</t>
   </si>
@@ -88,9 +97,6 @@
     <t>상자</t>
   </si>
   <si>
-    <t>배경 오브젝트 / 2D 오브젝트</t>
-  </si>
-  <si>
     <t>파괴가 가능한 오브젝트, 나무 박스의 형태를 띄고 있다.</t>
   </si>
   <si>
@@ -100,12 +106,6 @@
     <t>파괴가 가능한 오브젝트, 잡초의 형태를 띄고 있다.</t>
   </si>
   <si>
-    <t>자동차</t>
-  </si>
-  <si>
-    <t>파괴 가능한 오브젝트, 부서진 자동차의 외형을 띄고 있다. (종류는 3종류 정도?)</t>
-  </si>
-  <si>
     <t>돌</t>
   </si>
   <si>
@@ -173,22 +173,340 @@
   </si>
   <si>
     <t>멀리 보이는 건물들.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>오브젝트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>오브젝트</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>오브젝트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>오브젝트</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>나무</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>외곽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>오브젝트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / 2D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>오브젝트</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>앞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>쪽에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>보이는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>나무들</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -197,48 +515,45 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -428,21 +743,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="23.88"/>
-    <col customWidth="1" min="3" max="3" width="75.5"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="75.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,7 +772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -464,7 +783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -475,7 +794,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -486,7 +805,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -497,7 +816,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -508,7 +827,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -519,7 +838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -530,7 +849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -541,7 +860,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
@@ -553,23 +872,25 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.0"/>
-    <col customWidth="1" min="2" max="2" width="25.5"/>
-    <col customWidth="1" min="3" max="3" width="73.75"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="73.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -580,100 +901,92 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>37</v>
-      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="21.63"/>
-    <col customWidth="1" min="3" max="3" width="76.63"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="76.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -684,70 +997,72 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.63"/>
-    <col customWidth="1" min="2" max="2" width="22.38"/>
-    <col customWidth="1" min="3" max="3" width="76.5"/>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="76.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -756,29 +1071,41 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="B4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>